--- a/API_results.xlsx
+++ b/API_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,386 +454,345 @@
           <t>Time</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>League_ID</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Melbourne City</t>
+          <t>AFC Hermannstadt</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Brisbane Roar</t>
+          <t>Petrolul Ploiesti</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A-League</t>
+          <t>Liga I</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:35</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>188</v>
+          <t>12:30</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FC Tokyo</t>
+          <t>FC BW Linz</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>J1 League</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>98</v>
+          <t>12:30</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Estac Troyes</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Super League</t>
+          <t>Ligue 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>06:35</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>169</v>
+          <t>13:00</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Meizhou Kejia</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Super League</t>
+          <t>Ligue 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>06:35</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>169</v>
+          <t>13:00</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Martigues</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Super League</t>
+          <t>Ligue 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>169</v>
+          <t>13:00</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>PAU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Clermont Foot</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Ligue 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>333</v>
+          <t>13:00</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Amiens</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>El Gouna FC</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Ligue 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>233</v>
+          <t>13:00</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCM Gloria Buzău</t>
+          <t>RED Star FC 93</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Politehnica Iasi</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Liga I</t>
+          <t>Ligue 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>283</v>
+          <t>13:00</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ES Setif</t>
+          <t>Waalwijk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>186</v>
+          <t>13:00</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kooteepee</t>
+          <t>Medeama</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Dreams</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Veikkausliiga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>244</v>
+          <t>13:00</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ayacucho FC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>UTC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Primera División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>186</v>
+          <t>13:15</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Spartak Moscow</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>235</v>
+          <t>13:30</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>VfL Wolfsburg</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2. Bundesliga</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -843,502 +802,451 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>79</v>
+          <t>13:30</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SpVgg Greuther Fürth</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.FC Köln</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2. Bundesliga</t>
+          <t>Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>79</v>
+          <t>13:30</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Süper Lig</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>203</v>
+          <t>13:45</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HJK helsinki</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Veikkausliiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>244</v>
+          <t>13:45</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Charleroi</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Jupiler Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>233</v>
+          <t>13:45</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aalborg</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Superliga</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>119</v>
+          <t>14:00</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Olympique Safi</t>
+          <t>Norwich</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Botola Pro</t>
+          <t>Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>200</v>
+          <t>14:00</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AFC Hermannstadt</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Petrolul Ploiesti</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Liga I</t>
+          <t>Primera División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>283</v>
+          <t>14:00</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FC BW Linz</t>
+          <t>Riadi Salmi</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Botola Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>218</v>
+          <t>14:00</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Estac Troyes</t>
+          <t>GIL Vicente</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Guimaraes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ligue 2</t>
+          <t>Primeira Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>62</v>
+          <t>14:15</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Orsomarso</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ligue 2</t>
+          <t>Primera B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>62</v>
+          <t>15:30</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Martigues</t>
+          <t>Cultural Santa Rosa</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Sport Huancayo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ligue 2</t>
+          <t>Primera División</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>62</v>
+          <t>15:30</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PAU</t>
+          <t>Libertad Asuncion</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Clermont Foot</t>
+          <t>Nacional Asuncion</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ligue 2</t>
+          <t>Division Profesional - Apertura</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>62</v>
+          <t>16:30</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Amiens</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Independ. Rivadavia</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ligue 2</t>
+          <t>Liga Profesional Argentina</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>62</v>
+          <t>17:00</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RED Star FC 93</t>
+          <t>Patriotas</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ligue 2</t>
+          <t>Primera B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>62</v>
+          <t>18:00</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>Portuguesa FC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Waalwijk</t>
+          <t>Estudiantes de Merida FC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Primera División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>88</v>
+          <t>18:00</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Medeama</t>
+          <t>Llaneros</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dreams</t>
+          <t>Alianza Petrolera</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Primera A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>570</v>
+          <t>18:00</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ayacucho FC</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UTC</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1348,586 +1256,256 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>281</v>
+          <t>18:00</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Newells Old Boys</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Argentinos JRS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Segunda División</t>
+          <t>Liga Profesional Argentina</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>141</v>
+          <t>19:00</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Liga Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>78</v>
+          <t>19:00</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Municipal Liberia</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>CS Herediano</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serie B</t>
+          <t>Primera División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Costa-Rica</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>136</v>
+          <t>20:00</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Liga MX</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>61</v>
+          <t>20:00</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>CD Olimpia</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Liga Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>135</v>
+          <t>20:00</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Deportivo Cali</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Charleroi</t>
+          <t>Rionegro Aguilas</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jupiler Pro League</t>
+          <t>Primera A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>144</v>
+          <t>20:10</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>San Francisco FC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Herrera</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>La Liga</t>
+          <t>Liga Panameña de Fútbol</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>140</v>
+          <t>20:30</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Puntarenas FC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Norwich</t>
+          <t>San Carlos</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Championship</t>
+          <t>Primera División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Costa-Rica</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>40</v>
+          <t>21:00</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Mazatlán</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Guadalajara Chivas</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Primera División</t>
+          <t>Liga MX</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Riadi Salmi</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>CR Khemis Zemamra</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Botola Pro</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>GIL Vicente</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Guimaraes</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Primeira Liga</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Orsomarso</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Real Cartagena</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Primera B</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Cultural Santa Rosa</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Sport Huancayo</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Primera División</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Peru</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Libertad Asuncion</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Nacional Asuncion</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Division Profesional - Apertura</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Banfield</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Independ. Rivadavia</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Liga Profesional Argentina</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Patriotas</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Leones FC</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Primera B</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Portuguesa FC</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Estudiantes de Merida FC</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Primera División</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Llaneros</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Alianza Petrolera</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Primera A</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Independiente Petrolero</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Real Oruro</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Primera División</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>344</v>
+          <t>22:05</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/API_results.xlsx
+++ b/API_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,1051 +458,403 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AFC Hermannstadt</t>
+          <t>Libertad Asuncion</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Petrolul Ploiesti</t>
+          <t>Nacional Asuncion</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Liga I</t>
+          <t>Division Profesional - Apertura</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FC BW Linz</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Independ. Rivadavia</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Liga Profesional Argentina</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>17:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Estac Troyes</t>
+          <t>Patriotas</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ligue 2</t>
+          <t>Primera B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>18:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Portuguesa FC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Estudiantes de Merida FC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ligue 2</t>
+          <t>Primera División</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>18:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Martigues</t>
+          <t>Llaneros</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Alianza Petrolera</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ligue 2</t>
+          <t>Primera A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>18:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PAU</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Clermont Foot</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ligue 2</t>
+          <t>Primera División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>18:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Amiens</t>
+          <t>Newells Old Boys</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Argentinos JRS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ligue 2</t>
+          <t>Liga Profesional Argentina</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RED Star FC 93</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ligue 2</t>
+          <t>Liga Pro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>Municipal Liberia</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Waalwijk</t>
+          <t>CS Herediano</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Primera División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Costa-Rica</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Medeama</t>
+          <t>Necaxa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dreams</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Liga MX</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ayacucho FC</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UTC</t>
+          <t>CD Olimpia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Primera División</t>
+          <t>Liga Nacional</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>20:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Deportivo Cali</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Rionegro Aguilas</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Segunda División</t>
+          <t>Primera A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>20:10</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>San Francisco FC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Herrera</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bundesliga</t>
+          <t>Liga Panameña de Fútbol</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>20:30</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Puntarenas FC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>San Carlos</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serie B</t>
+          <t>Primera División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Costa-Rica</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>21:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Mazatlán</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Guadalajara Chivas</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>Liga MX</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>AC Milan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>KVC Westerlo</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Charleroi</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Jupiler Pro League</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>La Liga</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Burnley</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Norwich</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Real Tomayapo</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Primera División</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Riadi Salmi</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>CR Khemis Zemamra</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Botola Pro</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>GIL Vicente</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Guimaraes</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Primeira Liga</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Orsomarso</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Real Cartagena</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Primera B</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Cultural Santa Rosa</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Sport Huancayo</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Primera División</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Peru</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Libertad Asuncion</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Nacional Asuncion</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Division Profesional - Apertura</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Banfield</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Independ. Rivadavia</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Liga Profesional Argentina</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Patriotas</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Leones FC</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Primera B</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Portuguesa FC</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Estudiantes de Merida FC</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Primera División</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Llaneros</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Alianza Petrolera</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Primera A</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Independiente Petrolero</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Real Oruro</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Primera División</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Newells Old Boys</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Argentinos JRS</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Liga Profesional Argentina</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Emelec</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Libertad</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Liga Pro</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Municipal Liberia</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>CS Herediano</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Primera División</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Costa-Rica</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Necaxa</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Pachuca</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Liga MX</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>CD Olimpia</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Liga Nacional</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Honduras</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Deportivo Cali</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Rionegro Aguilas</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Primera A</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>San Francisco FC</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Herrera</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Liga Panameña de Fútbol</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Puntarenas FC</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>San Carlos</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Primera División</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Costa-Rica</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Mazatlán</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Guadalajara Chivas</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Liga MX</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
         <is>
           <t>22:05</t>
         </is>
